--- a/data/trans_orig/IP21-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP21-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24835</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>25939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44471</t>
+          <t>43470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81336</t>
+          <t>81627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93511</t>
+          <t>93935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98415</t>
+          <t>98174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110319</t>
+          <t>110458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183080</t>
+          <t>184081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200974</t>
+          <t>201612</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>245113</t>
+          <t>244719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251874</t>
+          <t>251836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238549</t>
+          <t>238657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248380</t>
+          <t>248439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>487456</t>
+          <t>487469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>498849</t>
+          <t>498894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122127</t>
+          <t>122195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127024</t>
+          <t>127022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131717</t>
+          <t>131696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139551</t>
+          <t>139424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>256813</t>
+          <t>257024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265573</t>
+          <t>265560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188556</t>
+          <t>188889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193501</t>
+          <t>193504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199233</t>
+          <t>199382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205360</t>
+          <t>205357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391374</t>
+          <t>391341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398758</t>
+          <t>398168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42986</t>
+          <t>43268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>47626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>72464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>647005</t>
+          <t>647104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>662654</t>
+          <t>662940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>679714</t>
+          <t>679432</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697388</t>
+          <t>698414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332598</t>
+          <t>1331257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356707</t>
+          <t>1356095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,82 +2695,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5995</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16866</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>25001</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>18281</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>33731</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10614</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5864</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16619</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>25001</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>18637</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>33569</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125497</t>
+          <t>126056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137541</t>
+          <t>137750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,82 +2808,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>133791</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>127539</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>138410</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>88,32%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>266165</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>257435</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>272885</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>91,41%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>88,42%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>93,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>133791</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>127786</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>138541</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>266165</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>257597</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>272529</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>88,47%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20305</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>17012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32305</t>
+          <t>33505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218899</t>
+          <t>218626</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229456</t>
+          <t>229318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248016</t>
+          <t>248143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>260216</t>
+          <t>259773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>472266</t>
+          <t>471066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>487366</t>
+          <t>487559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152699</t>
+          <t>152431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149086</t>
+          <t>149830</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157246</t>
+          <t>157258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>305342</t>
+          <t>305104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313216</t>
+          <t>313041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165937</t>
+          <t>165865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170683</t>
+          <t>170678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168354</t>
+          <t>168770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176150</t>
+          <t>176180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337119</t>
+          <t>337308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346299</t>
+          <t>346086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>37653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>43870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51365</t>
+          <t>49961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>76239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>673293</t>
+          <t>673738</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>690471</t>
+          <t>691059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>707350</t>
+          <t>706044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>724869</t>
+          <t>724665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1387002</t>
+          <t>1385066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1409940</t>
+          <t>1411344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118931</t>
+          <t>118506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127067</t>
+          <t>126862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113585</t>
+          <t>113960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121060</t>
+          <t>121393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235524</t>
+          <t>235584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246821</t>
+          <t>246631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198645</t>
+          <t>197996</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207080</t>
+          <t>206877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250942</t>
+          <t>250051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256883</t>
+          <t>256756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452435</t>
+          <t>452173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>462768</t>
+          <t>462670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180555</t>
+          <t>180274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>187023</t>
+          <t>187238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177881</t>
+          <t>177785</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186339</t>
+          <t>186367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>361905</t>
+          <t>361912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372253</t>
+          <t>372307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165791</t>
+          <t>165380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172002</t>
+          <t>171993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162353</t>
+          <t>162176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170895</t>
+          <t>170976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331082</t>
+          <t>331429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341995</t>
+          <t>341873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53651</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>673980</t>
+          <t>673887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>688227</t>
+          <t>688016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715114</t>
+          <t>715525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>730685</t>
+          <t>731211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394341</t>
+          <t>1393674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1415187</t>
+          <t>1415426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53293</t>
+          <t>53608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>56755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55584</t>
+          <t>55398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60533</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110999</t>
+          <t>110701</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116879</t>
+          <t>116591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>150317</t>
+          <t>149864</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157309</t>
+          <t>157362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175514</t>
+          <t>175618</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181283</t>
+          <t>181268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>328533</t>
+          <t>329094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>337384</t>
+          <t>337352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167147</t>
+          <t>167196</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172481</t>
+          <t>172480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204843</t>
+          <t>205095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>211688</t>
+          <t>211666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374770</t>
+          <t>375520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>383901</t>
+          <t>383640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271447</t>
+          <t>271553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294609</t>
+          <t>295802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304591</t>
+          <t>304628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>569098</t>
+          <t>569401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>579074</t>
+          <t>579079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30799</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>649591</t>
+          <t>649332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659921</t>
+          <t>659446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742456</t>
+          <t>741716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754495</t>
+          <t>754546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396097</t>
+          <t>1397058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1412632</t>
+          <t>1412289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP21-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP21-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10766</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23032</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17658</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12236</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24544</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13029</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23887</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16369</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10922</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23206</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25939</t>
+          <t>26072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43470</t>
+          <t>42904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>105011</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98348</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>110614</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88513</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>81627</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>93935</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>82284</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>93142</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>105011</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>98174</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>110458</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,51%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184081</t>
+          <t>184647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201612</t>
+          <t>201479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9342</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5265</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14741</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3908</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1369</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8486</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7724</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9342</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5317</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15099</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>244414</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>239015</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>248491</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>249297</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>244719</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>251836</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>245481</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>251893</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,46%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>244414</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>238657</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>248439</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>487469</t>
+          <t>486915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>498894</t>
+          <t>498544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1892</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8923</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1959</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5064</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9819</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>136808</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132592</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>139623</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>125589</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>122195</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>127022</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>122484</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>127023</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,46%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>136808</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>131696</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>139424</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>393</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257024</t>
+          <t>256107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265560</t>
+          <t>265694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6760</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1887</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5208</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6667</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>203313</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>199289</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205353</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>192210</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>188889</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>193504</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>189137</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>193502</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>203313</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>199382</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205357</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>589</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391341</t>
+          <t>390672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398168</t>
+          <t>398174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24714</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44527</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18081</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33917</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18554</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34256</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>24286</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>43268</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47626</t>
+          <t>47391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72464</t>
+          <t>71554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689546</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>678173</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>697986</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>978</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>655610</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>647104</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>662940</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>646765</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>662467</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,27%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>689546</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>679432</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>698414</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1331257</t>
+          <t>1332167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356095</t>
+          <t>1356330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6066</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16679</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14387</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9011</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20705</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9484</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20763</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10614</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5995</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16866</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>133791</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>127726</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>138339</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>132374</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>126056</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>137750</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>125998</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>137277</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>133791</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>127539</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>138410</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257435</t>
+          <t>257902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>272885</t>
+          <t>272612</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144405</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144405</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144405</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144405</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144405</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144405</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13384</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7964</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20385</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10960</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6932</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17624</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17340</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13384</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8548</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>20178</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>254937</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>247936</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>260357</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>225290</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>218626</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>229318</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>218910</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>229627</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,36%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>254937</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>248143</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>259773</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>471066</t>
+          <t>468996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>487559</t>
+          <t>487208</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268321</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268321</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268321</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268321</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268321</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268321</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8894</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1343</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4612</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4782</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3887</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8741</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149677</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157272</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155700</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152431</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>152261</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>149830</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>157258</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>444</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>305104</t>
+          <t>305968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313041</t>
+          <t>313584</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,74 +3699,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2244</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9890</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5472</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5460</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5337</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2437</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9847</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12406</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173280</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>168727</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>176373</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>169323</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>165865</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>170678</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>165877</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>170675</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>96,81%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>173280</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>168770</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>176180</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337308</t>
+          <t>337548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346086</t>
+          <t>346179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178617</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178617</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178617</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>178617</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>178617</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>178617</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24790</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44312</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28704</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20332</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37653</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20624</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>38603</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33222</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>25249</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>43870</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49961</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76239</t>
+          <t>75301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>716692</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>705602</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>725124</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>983</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>682687</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>673738</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>691059</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>672788</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>690767</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>716692</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>706044</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>724665</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1385066</t>
+          <t>1386004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1411344</t>
+          <t>1411510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749914</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749914</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749914</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749914</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749914</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 99,91%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2656</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10559</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6777</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3569</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11925</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12177</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5803</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2771</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10204</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118361</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>113605</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121508</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>123654</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>118506</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>126862</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>118254</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>126833</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,8%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118361</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>113960</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121393</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235584</t>
+          <t>235947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246631</t>
+          <t>246751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>130431</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>130431</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>130431</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7162</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7032</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3640</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3926</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12894</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8010</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>254792</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>250899</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>256873</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>203485</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>197996</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206877</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>197623</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>206591</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>254792</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>250051</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>256756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452173</t>
+          <t>451991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>462670</t>
+          <t>462479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2133</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10166</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4067</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1661</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8625</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5276</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2205</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10787</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>183296</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>178406</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>186439</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>184832</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>180274</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>187238</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>180499</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>187339</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,85%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>183296</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>177785</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>186367</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>361912</t>
+          <t>361130</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372307</t>
+          <t>371909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3084</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11254</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3352</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7921</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1256</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7317</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11872</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>167699</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>162794</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>170964</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>169949</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>165380</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>171993</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>165984</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>172045</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>167699</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>162176</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>170976</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331429</t>
+          <t>331920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341873</t>
+          <t>342069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14379</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29947</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15132</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29261</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15183</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29522</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13633</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29319</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32566</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>52655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>724147</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>714897</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>730465</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1026</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>681920</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>673887</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>688016</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>673626</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>687965</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>724147</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>715525</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>731211</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1393674</t>
+          <t>1395337</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1415426</t>
+          <t>1415811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>703148</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703148</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703148</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5333</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48037</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45204</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49585</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55732</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53608</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56755</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58743</t>
+          <t>50543</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55398</t>
+          <t>48415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60436</t>
+          <t>51472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114475</t>
+          <t>98580</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110701</t>
+          <t>95397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116591</t>
+          <t>100564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57095</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57095</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57095</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118539</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118539</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118539</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9435</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>154997</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>151496</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>156562</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>154764</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>149864</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>157362</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>179345</t>
+          <t>141095</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175618</t>
+          <t>136275</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181268</t>
+          <t>143910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>334109</t>
+          <t>296090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>329094</t>
+          <t>290768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>337352</t>
+          <t>299254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>197685</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>192796</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>199393</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>171014</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>167196</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>172480</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>209714</t>
+          <t>172676</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205095</t>
+          <t>169194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>211666</t>
+          <t>174056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>380729</t>
+          <t>370361</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>375520</t>
+          <t>365619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>383640</t>
+          <t>373215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9760</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4308</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3775</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9681</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>288787</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>282885</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>291365</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>274200</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>271553</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>255326</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>252245</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>256553</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>301708</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>295802</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>304628</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>678</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>575907</t>
+          <t>544112</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>569401</t>
+          <t>536713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>579079</t>
+          <t>547293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6636</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18992</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15592</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689504</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>681837</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>694193</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>655709</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>649332</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>659446</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>749511</t>
+          <t>619639</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741716</t>
+          <t>613898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754546</t>
+          <t>623645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,17 +8124,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1405221</t>
+          <t>1309143</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397058</t>
+          <t>1299538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1412289</t>
+          <t>1315343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426896</t>
+          <t>1329303</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426896</t>
+          <t>1329303</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426896</t>
+          <t>1329303</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
